--- a/artfynd/A 40910-2023 artfynd.xlsx
+++ b/artfynd/A 40910-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40910-2023 artfynd.xlsx
+++ b/artfynd/A 40910-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101112117</v>
+        <v>101112086</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438340.2058109645</v>
+        <v>438389</v>
       </c>
       <c r="R2" t="n">
-        <v>6672031.123443216</v>
+        <v>6672342</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-05-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101112086</v>
+        <v>101112263</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438388.2878424875</v>
+        <v>438437</v>
       </c>
       <c r="R3" t="n">
-        <v>6672341.296261442</v>
+        <v>6672080</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-05-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,54 +871,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101112248</v>
+        <v>104947195</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torrberget , Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438471.3863634269</v>
+        <v>438316</v>
       </c>
       <c r="R4" t="n">
-        <v>6671947.809178858</v>
+        <v>6671976</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +936,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +956,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101112263</v>
+        <v>104947261</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +979,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torrberget , Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438437.7249969923</v>
+        <v>438290</v>
       </c>
       <c r="R5" t="n">
-        <v>6672080.237161008</v>
+        <v>6672082</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1033,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1049,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104947261</v>
+        <v>101112248</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1081,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+          <t>Torrberget , Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438290.7259614334</v>
+        <v>438471</v>
       </c>
       <c r="R6" t="n">
-        <v>6672082.213192201</v>
+        <v>6671948</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,22 +1136,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,36 +1152,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Stefan Holmqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Stefan Holmqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104947310</v>
+        <v>104947516</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438310.1793498538</v>
+        <v>438471</v>
       </c>
       <c r="R7" t="n">
-        <v>6672053.523019033</v>
+        <v>6671970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,21 +1236,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1343,7 +1252,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>sälg/asp</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1361,15 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104947516</v>
+        <v>104947310</v>
       </c>
       <c r="B8" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438470.7741645313</v>
+        <v>438310</v>
       </c>
       <c r="R8" t="n">
-        <v>6671970.709119887</v>
+        <v>6672054</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,21 +1338,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1460,7 +1354,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>silverved av tall</t>
+          <t>sälg/asp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1475,6 +1369,206 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104947446</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>438472</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6672341</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>sälg/asp</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101112117</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Torrberget , Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438340</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6672031</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40910-2023 artfynd.xlsx
+++ b/artfynd/A 40910-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112263</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947195</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947261</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112248</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947516</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947310</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,8 +1614,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101112117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>